--- a/data/reports/2024-06-10/2024-06-10_duplicates.xlsx
+++ b/data/reports/2024-06-10/2024-06-10_duplicates.xlsx
@@ -145,7 +145,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -161,28 +161,28 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -225,10 +225,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,6 +318,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -340,13 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -469,10 +469,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -483,16 +493,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007488</t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -606,15 +606,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -622,24 +640,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -670,7 +670,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -681,32 +681,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -726,6 +700,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -754,7 +754,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -764,6 +764,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -780,12 +786,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005569</t>
@@ -836,7 +836,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
+    <t>RMD0005297</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -849,6 +849,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
+  </si>
+  <si>
     <t>Syed Omar Farooq Shah</t>
   </si>
   <si>
@@ -858,13 +864,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -878,6 +878,22 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>187 Plymouth Ave
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -891,23 +907,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>187 Plymouth Ave
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -993,7 +993,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1003,16 +1003,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1022,6 +1022,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1035,12 +1041,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1074,7 +1074,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1084,12 +1084,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1097,6 +1091,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008611</t>
   </si>
   <si>
@@ -1116,25 +1116,25 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008610</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -6179,16 +6179,28 @@
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -6196,16 +6208,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -6229,28 +6241,16 @@
         <v>46</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6527,9 +6527,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
@@ -6540,14 +6542,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6574,7 +6578,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6583,13 +6587,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
@@ -6600,9 +6602,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6621,55 +6621,41 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6681,32 +6667,46 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6732,54 +6732,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6796,33 +6782,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -6988,13 +6988,13 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>127</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7473,55 +7473,61 @@
         <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1">
         <v>30758643</v>
@@ -7533,34 +7539,28 @@
         <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>194</v>
@@ -7570,10 +7570,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -7602,7 +7602,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7648,7 +7648,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -7666,14 +7666,14 @@
         <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -7715,45 +7715,33 @@
       <c r="I33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1">
         <v>31064850</v>
@@ -7771,30 +7759,42 @@
         <v>209</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>30</v>
@@ -7926,48 +7926,34 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B38" s="1">
         <v>31124688</v>
@@ -7986,25 +7972,39 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -8155,45 +8155,33 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31294614</v>
@@ -8213,24 +8201,36 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8262,48 +8262,42 @@
       <c r="H43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1">
         <v>31356652</v>
@@ -8324,14 +8318,18 @@
         <v>268</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>277</v>
       </c>
@@ -8339,22 +8337,24 @@
         <v>27</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V44" s="1" t="s">
         <v>278</v>
       </c>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>30</v>
@@ -8680,9 +8680,15 @@
       <c r="F51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -8726,15 +8732,9 @@
       <c r="F52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -8773,55 +8773,41 @@
         <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1">
         <v>31445216</v>
@@ -8833,32 +8819,46 @@
         <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8993,7 +8993,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="1">
         <v>31457815</v>
@@ -9039,7 +9039,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9124,38 +9124,50 @@
         <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R60" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1">
         <v>31475270</v>
@@ -9170,41 +9182,29 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9251,7 +9251,7 @@
         <v>354</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>30</v>
@@ -9357,7 +9357,7 @@
         <v>366</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>30</v>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>30</v>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>30</v>
@@ -9851,13 +9851,13 @@
         <v>27</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>407</v>
@@ -9937,7 +9937,7 @@
       </c>
       <c r="P75" s="1"/>
       <c r="Q75" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R75" s="1" t="s">
         <v>30</v>
@@ -10001,7 +10001,7 @@
         <v>425</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>26</v>
@@ -10134,7 +10134,7 @@
         <v>245</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>433</v>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="P79" s="1"/>
       <c r="Q79" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>30</v>
@@ -10236,7 +10236,7 @@
         <v>30</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>28</v>
@@ -10679,10 +10679,10 @@
         <v>490</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>489</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="P89" s="1"/>
       <c r="Q89" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R89" s="1" t="s">
         <v>30</v>
@@ -10733,7 +10733,7 @@
         <v>495</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>496</v>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>30</v>
@@ -10871,7 +10871,7 @@
         <v>513</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R92" s="1" t="s">
         <v>26</v>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="P94" s="1"/>
       <c r="Q94" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R94" s="1" t="s">
         <v>26</v>
@@ -11128,7 +11128,7 @@
         <v>30</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
@@ -11137,21 +11137,21 @@
         <v>540</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>541</v>
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O97" s="1" t="s">
         <v>542</v>
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R97" s="1" t="s">
         <v>30</v>
@@ -11240,7 +11240,7 @@
         <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -11258,14 +11258,14 @@
         <v>552</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>553</v>
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>30</v>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>30</v>
@@ -11361,13 +11361,13 @@
         <v>27</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>564</v>
@@ -11376,7 +11376,7 @@
         <v>59</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>563</v>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>30</v>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>26</v>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>30</v>
@@ -11812,7 +11812,7 @@
         <v>293</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>616</v>
@@ -11854,7 +11854,7 @@
         <v>30</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>30</v>
@@ -11956,7 +11956,7 @@
         <v>629</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>626</v>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="P114" s="1"/>
       <c r="Q114" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R114" s="1" t="s">
         <v>30</v>
@@ -12193,7 +12193,7 @@
       </c>
       <c r="P116" s="1"/>
       <c r="Q116" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R116" s="1" t="s">
         <v>30</v>
@@ -12286,7 +12286,7 @@
         <v>666</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>662</v>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R121" s="1" t="s">
         <v>30</v>
@@ -12624,7 +12624,7 @@
         <v>59</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M124" s="1" t="s">
         <v>703</v>
@@ -12834,7 +12834,7 @@
         <v>245</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>722</v>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>30</v>
@@ -12984,7 +12984,7 @@
         <v>30</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
@@ -13153,7 +13153,7 @@
       </c>
       <c r="P134" s="1"/>
       <c r="Q134" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R134" s="1" t="s">
         <v>30</v>
@@ -13248,7 +13248,7 @@
         <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>28</v>
@@ -13272,7 +13272,7 @@
         <v>762</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O136" s="1" t="s">
         <v>765</v>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P138" s="1"/>
       <c r="Q138" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R138" s="1" t="s">
         <v>30</v>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R140" s="1" t="s">
         <v>30</v>
@@ -13562,7 +13562,7 @@
         <v>798</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>796</v>
@@ -13736,7 +13736,7 @@
         <v>819</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M144" s="1" t="s">
         <v>816</v>
@@ -13836,7 +13836,7 @@
         <v>30</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
@@ -13854,14 +13854,14 @@
         <v>830</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O146" s="1" t="s">
         <v>831</v>
       </c>
       <c r="P146" s="1"/>
       <c r="Q146" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R146" s="1" t="s">
         <v>30</v>
@@ -13890,7 +13890,7 @@
         <v>30</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>834</v>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="P148" s="1"/>
       <c r="Q148" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R148" s="1" t="s">
         <v>30</v>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R149" s="1" t="s">
         <v>30</v>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="P156" s="1"/>
       <c r="Q156" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R156" s="1" t="s">
         <v>30</v>
@@ -14420,7 +14420,7 @@
         <v>887</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M157" s="1"/>
       <c r="N157" s="1" t="s">
@@ -14473,7 +14473,7 @@
         <v>893</v>
       </c>
       <c r="K158" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L158" s="1" t="s">
         <v>894</v>
@@ -14589,7 +14589,7 @@
         <v>906</v>
       </c>
       <c r="Q160" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R160" s="1" t="s">
         <v>26</v>
@@ -14623,7 +14623,7 @@
         <v>27</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>26</v>
@@ -14722,7 +14722,7 @@
         <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>28</v>
@@ -14746,14 +14746,14 @@
         <v>922</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O163" s="1" t="s">
         <v>923</v>
       </c>
       <c r="P163" s="1"/>
       <c r="Q163" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R163" s="1" t="s">
         <v>30</v>
@@ -14787,7 +14787,7 @@
         <v>27</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>927</v>
@@ -14815,7 +14815,7 @@
       </c>
       <c r="P164" s="1"/>
       <c r="Q164" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>30</v>
@@ -14846,7 +14846,7 @@
         <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
@@ -14858,11 +14858,11 @@
         <v>59</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M165" s="1"/>
       <c r="N165" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O165" s="1" t="s">
         <v>935</v>
@@ -15050,7 +15050,7 @@
         <v>30</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
@@ -15059,21 +15059,21 @@
         <v>952</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L169" s="1" t="s">
         <v>203</v>
       </c>
       <c r="M169" s="1"/>
       <c r="N169" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>953</v>
       </c>
       <c r="P169" s="1"/>
       <c r="Q169" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R169" s="1" t="s">
         <v>30</v>
@@ -15158,7 +15158,7 @@
         <v>59</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M171" s="1"/>
       <c r="N171" s="1" t="s">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="P171" s="1"/>
       <c r="Q171" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>30</v>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="P172" s="1"/>
       <c r="Q172" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>26</v>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>30</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>30</v>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>30</v>
@@ -15512,7 +15512,7 @@
         <v>1003</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>1004</v>
@@ -15663,13 +15663,13 @@
         <v>27</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>1020</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J180" s="1" t="s">
         <v>1021</v>
@@ -15678,7 +15678,7 @@
         <v>1022</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M180" s="1" t="s">
         <v>1019</v>
@@ -15727,13 +15727,13 @@
         <v>27</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>1028</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P183" s="1"/>
       <c r="Q183" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R183" s="1" t="s">
         <v>30</v>
@@ -16071,13 +16071,13 @@
         <v>27</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H187" s="1" t="s">
         <v>1062</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="P189" s="1"/>
       <c r="Q189" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>26</v>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="P190" s="1"/>
       <c r="Q190" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R190" s="1" t="s">
         <v>26</v>
@@ -16312,7 +16312,7 @@
         <v>165</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>1092</v>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="P191" s="1"/>
       <c r="Q191" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>30</v>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>30</v>
@@ -16486,7 +16486,7 @@
         <v>1113</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M194" s="1" t="s">
         <v>1114</v>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R194" s="1" t="s">
         <v>30</v>
@@ -16750,7 +16750,7 @@
         <v>30</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
@@ -16762,18 +16762,18 @@
         <v>442</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M199" s="1"/>
       <c r="N199" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O199" s="1" t="s">
         <v>1144</v>
       </c>
       <c r="P199" s="1"/>
       <c r="Q199" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R199" s="1" t="s">
         <v>30</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="P201" s="1"/>
       <c r="Q201" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R201" s="1" t="s">
         <v>30</v>
@@ -16930,7 +16930,7 @@
         <v>1160</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M202" s="1"/>
       <c r="N202" s="1" t="s">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="P205" s="1"/>
       <c r="Q205" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>30</v>
@@ -17168,7 +17168,7 @@
         <v>59</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M206" s="1" t="s">
         <v>1187</v>
@@ -17181,7 +17181,7 @@
       </c>
       <c r="P206" s="1"/>
       <c r="Q206" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R206" s="1" t="s">
         <v>30</v>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="P208" s="1"/>
       <c r="Q208" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R208" s="1" t="s">
         <v>30</v>
@@ -17343,7 +17343,7 @@
         <v>1206</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L209" s="1" t="s">
         <v>1207</v>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="P210" s="1"/>
       <c r="Q210" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>30</v>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>30</v>
@@ -17537,7 +17537,7 @@
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R212" s="1" t="s">
         <v>30</v>
@@ -17572,16 +17572,16 @@
         <v>30</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>1240</v>
@@ -17596,7 +17596,7 @@
         <v>1239</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>1242</v>
@@ -17638,7 +17638,7 @@
         <v>30</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>1245</v>
@@ -17658,7 +17658,7 @@
         <v>1239</v>
       </c>
       <c r="N214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O214" s="1" t="s">
         <v>1242</v>
@@ -17713,10 +17713,10 @@
         <v>1252</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M215" s="1" t="s">
         <v>1253</v>
@@ -17847,7 +17847,7 @@
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R217" s="1" t="s">
         <v>30</v>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>30</v>
@@ -17947,7 +17947,7 @@
         <v>1204</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
@@ -17971,7 +17971,7 @@
       </c>
       <c r="P219" s="1"/>
       <c r="Q219" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R219" s="1" t="s">
         <v>30</v>
@@ -18070,7 +18070,7 @@
         <v>1285</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>1286</v>
@@ -18130,7 +18130,7 @@
         <v>1293</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M222" s="1" t="s">
         <v>1294</v>
@@ -18143,7 +18143,7 @@
       </c>
       <c r="P222" s="1"/>
       <c r="Q222" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R222" s="1" t="s">
         <v>30</v>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="P223" s="1"/>
       <c r="Q223" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R223" s="1" t="s">
         <v>26</v>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>26</v>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>30</v>
@@ -18385,7 +18385,7 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R226" s="1" t="s">
         <v>30</v>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="P227" s="1"/>
       <c r="Q227" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R227" s="1" t="s">
         <v>30</v>
@@ -18509,7 +18509,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>30</v>
@@ -18620,7 +18620,7 @@
         <v>165</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M230" s="1" t="s">
         <v>1351</v>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>30</v>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R231" s="1" t="s">
         <v>30</v>
@@ -18731,13 +18731,13 @@
         <v>27</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H232" s="1" t="s">
         <v>1364</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>1365</v>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="P232" s="1"/>
       <c r="Q232" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R232" s="1" t="s">
         <v>30</v>
@@ -18812,7 +18812,7 @@
         <v>629</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M233" s="1" t="s">
         <v>1374</v>
@@ -18825,7 +18825,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>30</v>
@@ -18939,7 +18939,7 @@
         <v>1391</v>
       </c>
       <c r="K235" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L235" s="1" t="s">
         <v>1392</v>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="P235" s="1"/>
       <c r="Q235" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R235" s="1" t="s">
         <v>30</v>
@@ -19021,7 +19021,7 @@
       </c>
       <c r="P236" s="1"/>
       <c r="Q236" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R236" s="1" t="s">
         <v>30</v>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="P237" s="1"/>
       <c r="Q237" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R237" s="1" t="s">
         <v>30</v>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>30</v>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>30</v>
@@ -19380,7 +19380,7 @@
         <v>1435</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M242" s="1" t="s">
         <v>1440</v>
@@ -19437,10 +19437,10 @@
         <v>1446</v>
       </c>
       <c r="K243" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M243" s="1" t="s">
         <v>1445</v>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P243" s="1"/>
       <c r="Q243" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R243" s="1" t="s">
         <v>30</v>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="P244" s="1"/>
       <c r="Q244" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R244" s="1" t="s">
         <v>26</v>
@@ -19609,13 +19609,13 @@
         <v>27</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>1457</v>
@@ -19699,7 +19699,7 @@
         <v>1471</v>
       </c>
       <c r="Q247" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R247" s="1" t="s">
         <v>30</v>
@@ -19812,7 +19812,7 @@
         <v>293</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1484</v>
@@ -19825,7 +19825,7 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R249" s="1" t="s">
         <v>30</v>
@@ -19874,7 +19874,7 @@
         <v>293</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M250" s="1" t="s">
         <v>1484</v>
@@ -19887,7 +19887,7 @@
       </c>
       <c r="P250" s="1"/>
       <c r="Q250" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>30</v>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="P252" s="1"/>
       <c r="Q252" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R252" s="1" t="s">
         <v>30</v>
@@ -20416,7 +20416,7 @@
         <v>1550</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M259" s="1" t="s">
         <v>1551</v>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="P259" s="1"/>
       <c r="Q259" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>30</v>
@@ -20480,7 +20480,7 @@
         <v>1550</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>1556</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>30</v>
@@ -20604,7 +20604,7 @@
         <v>572</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M262" s="1" t="s">
         <v>1572</v>
@@ -20617,7 +20617,7 @@
       </c>
       <c r="P262" s="1"/>
       <c r="Q262" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R262" s="1" t="s">
         <v>30</v>
@@ -20653,13 +20653,13 @@
         <v>27</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>1578</v>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>30</v>
@@ -20728,7 +20728,7 @@
         <v>293</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M264" s="1" t="s">
         <v>1586</v>
@@ -20792,7 +20792,7 @@
         <v>1595</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M265" s="1" t="s">
         <v>1596</v>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R265" s="1" t="s">
         <v>30</v>
@@ -20865,7 +20865,7 @@
       </c>
       <c r="P266" s="1"/>
       <c r="Q266" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R266" s="1" t="s">
         <v>30</v>
@@ -20916,7 +20916,7 @@
         <v>629</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1608</v>
@@ -20978,7 +20978,7 @@
         <v>629</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1608</v>
@@ -21040,7 +21040,7 @@
         <v>59</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1620</v>
@@ -21104,7 +21104,7 @@
         <v>59</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>1627</v>
@@ -21155,13 +21155,13 @@
         <v>209</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H271" s="1" t="s">
         <v>1636</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>1637</v>
@@ -21185,7 +21185,7 @@
         <v>1641</v>
       </c>
       <c r="Q271" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>30</v>
@@ -21223,13 +21223,13 @@
         <v>209</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H272" s="1" t="s">
         <v>1636</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>1637</v>
@@ -21253,7 +21253,7 @@
         <v>1641</v>
       </c>
       <c r="Q272" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>30</v>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>30</v>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>30</v>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>30</v>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="P276" s="1"/>
       <c r="Q276" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>30</v>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>30</v>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="P280" s="1"/>
       <c r="Q280" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R280" s="1" t="s">
         <v>30</v>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="P283" s="1"/>
       <c r="Q283" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R283" s="1" t="s">
         <v>30</v>
@@ -21985,7 +21985,7 @@
         <v>1731</v>
       </c>
       <c r="Q284" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R284" s="1" t="s">
         <v>30</v>
@@ -22020,7 +22020,7 @@
         <v>30</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>1736</v>
@@ -22034,20 +22034,20 @@
         <v>1738</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M285" s="1" t="s">
         <v>1735</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O285" s="1" t="s">
         <v>1739</v>
       </c>
       <c r="P285" s="1"/>
       <c r="Q285" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R285" s="1" t="s">
         <v>30</v>
@@ -22080,7 +22080,7 @@
         <v>30</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G286" s="1"/>
       <c r="H286" s="1"/>
@@ -22092,20 +22092,20 @@
         <v>1743</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M286" s="1" t="s">
         <v>1735</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O286" s="1" t="s">
         <v>1744</v>
       </c>
       <c r="P286" s="1"/>
       <c r="Q286" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R286" s="1" t="s">
         <v>30</v>
